--- a/p2p_breakdown.xlsx
+++ b/p2p_breakdown.xlsx
@@ -501,34 +501,44 @@
         <v>0</v>
       </c>
       <c r="B2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1250</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.6687</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>70.55498488001942</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="3">
@@ -536,34 +546,44 @@
         <v>1</v>
       </c>
       <c r="B3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1250</v>
+      </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5802</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.275</v>
       </c>
       <c r="M3" t="n">
-        <v>68.99673062879872</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -571,34 +591,44 @@
         <v>2</v>
       </c>
       <c r="B4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1250</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.6067</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.131</v>
       </c>
       <c r="M4" t="n">
-        <v>68.08178935328505</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -606,34 +636,44 @@
         <v>3</v>
       </c>
       <c r="B5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1250</v>
+      </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6382</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.977</v>
       </c>
       <c r="M5" t="n">
-        <v>67.82266835883961</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -641,34 +681,44 @@
         <v>4</v>
       </c>
       <c r="B6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1250</v>
+      </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.6934</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.086</v>
       </c>
       <c r="M6" t="n">
-        <v>69.44527157761993</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="7">
@@ -676,34 +726,44 @@
         <v>5</v>
       </c>
       <c r="B7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>1.3921</v>
+      </c>
+      <c r="D7" t="n">
+        <v>978.78</v>
+      </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.5225</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004473635257480174</v>
+        <v>2.952</v>
       </c>
       <c r="M7" t="n">
-        <v>75.94678391694735</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -711,34 +771,44 @@
         <v>6</v>
       </c>
       <c r="B8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>1.4179</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1250</v>
+      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A1;A2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>A3;A4;A5;A6</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.9496</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.733640650631941</v>
+        <v>5.033</v>
       </c>
       <c r="M8" t="n">
-        <v>84.06720371432245</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +816,44 @@
         <v>7</v>
       </c>
       <c r="B9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>1.497</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1114.98</v>
+      </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A1;A2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>A3;A4;A5;A6</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9135</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.7623</v>
       </c>
       <c r="L9" t="n">
-        <v>8.908664638099914</v>
+        <v>5.892</v>
       </c>
       <c r="M9" t="n">
-        <v>112.7267135567679</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="10">
@@ -781,34 +861,44 @@
         <v>8</v>
       </c>
       <c r="B10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1.8231</v>
+      </c>
+      <c r="D10" t="n">
+        <v>935.9400000000001</v>
+      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A1;A2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A3;A4;A5;A6</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.9049</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.4471</v>
       </c>
       <c r="L10" t="n">
-        <v>19.04586272618084</v>
+        <v>6.198</v>
       </c>
       <c r="M10" t="n">
-        <v>125.4450889700644</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="11">
@@ -819,41 +909,41 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5325</v>
+        <v>2.238</v>
       </c>
       <c r="D11" t="n">
-        <v>475.41</v>
+        <v>427.02</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2306</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0563</v>
+        <v>0.4489</v>
       </c>
       <c r="L11" t="n">
-        <v>27.602</v>
+        <v>7.207</v>
       </c>
       <c r="M11" t="n">
-        <v>119.677</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
@@ -864,41 +954,41 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>8.2667</v>
+        <v>3.4395</v>
       </c>
       <c r="D12" t="n">
-        <v>364.23</v>
+        <v>471.79</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3033</v>
+        <v>0.902</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5447</v>
+        <v>0.3701</v>
       </c>
       <c r="L12" t="n">
-        <v>32.945</v>
+        <v>8.686</v>
       </c>
       <c r="M12" t="n">
-        <v>108.621</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -909,41 +999,41 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10.1136</v>
+        <v>4.103</v>
       </c>
       <c r="D13" t="n">
-        <v>382.67</v>
+        <v>378.93</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3323</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.9792</v>
       </c>
       <c r="K13" t="n">
-        <v>0.445</v>
+        <v>0.5336</v>
       </c>
       <c r="L13" t="n">
-        <v>34.04</v>
+        <v>9.76</v>
       </c>
       <c r="M13" t="n">
-        <v>102.439</v>
+        <v>9.555999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -954,41 +1044,41 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>11.5903</v>
+        <v>3.6794</v>
       </c>
       <c r="D14" t="n">
-        <v>453.38</v>
+        <v>332.01</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3938</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.8971</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.6162</v>
       </c>
       <c r="L14" t="n">
-        <v>33.884</v>
+        <v>10.378</v>
       </c>
       <c r="M14" t="n">
-        <v>86.03700000000001</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="15">
@@ -999,41 +1089,41 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>11.3877</v>
+        <v>4.2764</v>
       </c>
       <c r="D15" t="n">
-        <v>451.35</v>
+        <v>397.06</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4112</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.9294</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0738</v>
+        <v>0.5017</v>
       </c>
       <c r="L15" t="n">
-        <v>32.373</v>
+        <v>10.122</v>
       </c>
       <c r="M15" t="n">
-        <v>78.73</v>
+        <v>9.407999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1044,41 +1134,41 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>7.8429</v>
+        <v>4.3507</v>
       </c>
       <c r="D16" t="n">
-        <v>456.08</v>
+        <v>397.48</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2878</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0482</v>
+        <v>0.5009</v>
       </c>
       <c r="L16" t="n">
-        <v>28.272</v>
+        <v>9.647</v>
       </c>
       <c r="M16" t="n">
-        <v>98.235</v>
+        <v>9.468</v>
       </c>
     </row>
     <row r="17">
@@ -1089,41 +1179,41 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8804</v>
+        <v>3.3582</v>
       </c>
       <c r="D17" t="n">
-        <v>476.32</v>
+        <v>224.76</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A2;A3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Mariana;UCC;HUDN;Cesmag</t>
+          <t>A1;A4;A5;A6</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1879</v>
+        <v>0.8817</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0612</v>
+        <v>0.805</v>
       </c>
       <c r="L17" t="n">
-        <v>21.051</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>112.046</v>
+        <v>9.818</v>
       </c>
     </row>
     <row r="18">
@@ -1131,34 +1221,44 @@
         <v>16</v>
       </c>
       <c r="B18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>2.02</v>
+      </c>
+      <c r="D18" t="n">
+        <v>940.17</v>
+      </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A1;A2;A3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>A4;A5;A6</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.9364</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.4545</v>
       </c>
       <c r="L18" t="n">
-        <v>11.68881585247795</v>
+        <v>6.864</v>
       </c>
       <c r="M18" t="n">
-        <v>123.0593173455423</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="19">
@@ -1166,34 +1266,44 @@
         <v>17</v>
       </c>
       <c r="B19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>0.5727</v>
+      </c>
+      <c r="D19" t="n">
+        <v>299.41</v>
+      </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A1;A3;A4;A5;A6</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.8138</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.6736</v>
       </c>
       <c r="L19" t="n">
-        <v>2.885785935375627</v>
+        <v>5.998</v>
       </c>
       <c r="M19" t="n">
-        <v>134.3470227508151</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="20">
@@ -1201,34 +1311,44 @@
         <v>18</v>
       </c>
       <c r="B20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>366.42</v>
+      </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A1;A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.6972</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.5556</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04233802905192913</v>
+        <v>4.037</v>
       </c>
       <c r="M20" t="n">
-        <v>122.105414177294</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21">
@@ -1236,34 +1356,44 @@
         <v>19</v>
       </c>
       <c r="B21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>0.8776</v>
+      </c>
+      <c r="D21" t="n">
+        <v>421.79</v>
+      </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A1;A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.5419</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.4581</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.878</v>
       </c>
       <c r="M21" t="n">
-        <v>105.7007215392626</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="22">
@@ -1271,34 +1401,44 @@
         <v>20</v>
       </c>
       <c r="B22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>0.7396</v>
+      </c>
+      <c r="D22" t="n">
+        <v>248.93</v>
+      </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>A1;A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.6212</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.7624</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
-        <v>94.04497206292893</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="23">
@@ -1306,34 +1446,44 @@
         <v>21</v>
       </c>
       <c r="B23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>1.5412</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1250</v>
+      </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.8202</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.141</v>
       </c>
       <c r="M23" t="n">
-        <v>82.9576134139716</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="24">
@@ -1341,34 +1491,44 @@
         <v>22</v>
       </c>
       <c r="B24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>1.0831</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1136.18</v>
+      </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.8982</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.7996</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.883</v>
       </c>
       <c r="M24" t="n">
-        <v>74.88639463695215</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="25">
@@ -1376,34 +1536,44 @@
         <v>23</v>
       </c>
       <c r="B25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1250</v>
+      </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A1;A4</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A2;A3;A5;A6</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.268</v>
       </c>
       <c r="M25" t="n">
-        <v>72.58028434938056</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,29 +1634,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8838</v>
+        <v>0.1801</v>
       </c>
       <c r="E2" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F2" t="n">
-        <v>574.47</v>
+        <v>225.08</v>
       </c>
       <c r="G2" t="n">
-        <v>327.01</v>
+        <v>204.55</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1494,29 +1664,29 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F3" t="n">
-        <v>565.1799999999999</v>
+        <v>112.54</v>
       </c>
       <c r="G3" t="n">
-        <v>321.72</v>
+        <v>102.27</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1524,119 +1694,119 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8854</v>
+        <v>0.0413</v>
       </c>
       <c r="E4" t="n">
-        <v>326.96</v>
+        <v>1250</v>
       </c>
       <c r="F4" t="n">
-        <v>289.47</v>
+        <v>51.58</v>
       </c>
       <c r="G4" t="n">
-        <v>41.57</v>
+        <v>46.88</v>
       </c>
       <c r="H4" t="n">
-        <v>286.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8939</v>
+        <v>0.0413</v>
       </c>
       <c r="E5" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F5" t="n">
-        <v>250.28</v>
+        <v>51.58</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>46.88</v>
       </c>
       <c r="H5" t="n">
-        <v>330.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.098</v>
+        <v>0.2999</v>
       </c>
       <c r="E6" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F6" t="n">
-        <v>587.4400000000001</v>
+        <v>374.92</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>340.73</v>
       </c>
       <c r="H6" t="n">
-        <v>776.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.8818</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F7" t="n">
-        <v>1223.2</v>
+        <v>187.46</v>
       </c>
       <c r="G7" t="n">
-        <v>696.28</v>
+        <v>170.37</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1644,119 +1814,119 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.1377</v>
+        <v>0.0687</v>
       </c>
       <c r="E8" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F8" t="n">
-        <v>598.55</v>
+        <v>85.92</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>78.08</v>
       </c>
       <c r="H8" t="n">
-        <v>790.9400000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.1491</v>
+        <v>0.0687</v>
       </c>
       <c r="E9" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F9" t="n">
-        <v>601.76</v>
+        <v>85.92</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>78.08</v>
       </c>
       <c r="H9" t="n">
-        <v>795.1799999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.5415</v>
+        <v>0.1351</v>
       </c>
       <c r="E10" t="n">
-        <v>355.46</v>
+        <v>1250</v>
       </c>
       <c r="F10" t="n">
-        <v>903.42</v>
+        <v>168.82</v>
       </c>
       <c r="G10" t="n">
-        <v>191.79</v>
+        <v>153.43</v>
       </c>
       <c r="H10" t="n">
-        <v>748.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.288</v>
+        <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F11" t="n">
-        <v>1487.18</v>
+        <v>112.55</v>
       </c>
       <c r="G11" t="n">
-        <v>846.55</v>
+        <v>102.28</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1764,119 +1934,119 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.6554</v>
+        <v>0.0413</v>
       </c>
       <c r="E12" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F12" t="n">
-        <v>743.52</v>
+        <v>51.58</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>46.88</v>
       </c>
       <c r="H12" t="n">
-        <v>982.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.6287</v>
+        <v>0.0413</v>
       </c>
       <c r="E13" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F13" t="n">
-        <v>736.02</v>
+        <v>51.58</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>46.88</v>
       </c>
       <c r="H13" t="n">
-        <v>972.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.152</v>
+        <v>0.2249</v>
       </c>
       <c r="E14" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F14" t="n">
-        <v>882.5700000000001</v>
+        <v>281.18</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>255.53</v>
       </c>
       <c r="H14" t="n">
-        <v>1166.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.6198</v>
+        <v>0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F15" t="n">
-        <v>1702.87</v>
+        <v>187.45</v>
       </c>
       <c r="G15" t="n">
-        <v>969.3200000000001</v>
+        <v>170.36</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1884,59 +2054,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.0071</v>
+        <v>0.0687</v>
       </c>
       <c r="E16" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F16" t="n">
-        <v>841.98</v>
+        <v>85.92</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>78.08</v>
       </c>
       <c r="H16" t="n">
-        <v>1112.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.8114</v>
+        <v>0.0687</v>
       </c>
       <c r="E17" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F17" t="n">
-        <v>1827.44</v>
+        <v>85.92</v>
       </c>
       <c r="G17" t="n">
-        <v>1040.23</v>
+        <v>78.08</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1944,59 +2114,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.0954</v>
+        <v>0.1351</v>
       </c>
       <c r="E18" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F18" t="n">
-        <v>866.71</v>
+        <v>168.83</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>153.43</v>
       </c>
       <c r="H18" t="n">
-        <v>1145.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.5727</v>
+        <v>0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F19" t="n">
-        <v>1672.29</v>
+        <v>112.55</v>
       </c>
       <c r="G19" t="n">
-        <v>951.92</v>
+        <v>102.29</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2004,29 +2174,29 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.701</v>
+        <v>0.0413</v>
       </c>
       <c r="E20" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F20" t="n">
-        <v>1755.63</v>
+        <v>51.59</v>
       </c>
       <c r="G20" t="n">
-        <v>999.36</v>
+        <v>46.88</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2034,89 +2204,89 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.0186</v>
+        <v>0.0413</v>
       </c>
       <c r="E21" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F21" t="n">
-        <v>845.21</v>
+        <v>51.59</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>46.88</v>
       </c>
       <c r="H21" t="n">
-        <v>1116.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.0374</v>
+        <v>0.2249</v>
       </c>
       <c r="E22" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F22" t="n">
-        <v>570.48</v>
+        <v>281.17</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>255.53</v>
       </c>
       <c r="H22" t="n">
-        <v>753.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.8017</v>
+        <v>0.15</v>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F23" t="n">
-        <v>1171.13</v>
+        <v>187.45</v>
       </c>
       <c r="G23" t="n">
-        <v>666.64</v>
+        <v>170.35</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2124,29 +2294,29 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.9307</v>
+        <v>0.0687</v>
       </c>
       <c r="E24" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F24" t="n">
-        <v>1254.95</v>
+        <v>85.91</v>
       </c>
       <c r="G24" t="n">
-        <v>714.35</v>
+        <v>78.08</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2154,89 +2324,89 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cesmag</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.073</v>
+        <v>0.0687</v>
       </c>
       <c r="E25" t="n">
-        <v>280</v>
+        <v>1250</v>
       </c>
       <c r="F25" t="n">
-        <v>580.4400000000001</v>
+        <v>85.91</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>78.08</v>
       </c>
       <c r="H25" t="n">
-        <v>767.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4708</v>
+        <v>0.1351</v>
       </c>
       <c r="E26" t="n">
-        <v>326.96</v>
+        <v>1250</v>
       </c>
       <c r="F26" t="n">
-        <v>153.92</v>
+        <v>168.83</v>
       </c>
       <c r="G26" t="n">
-        <v>22.11</v>
+        <v>153.43</v>
       </c>
       <c r="H26" t="n">
-        <v>152.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.4682</v>
+        <v>0.09</v>
       </c>
       <c r="E27" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F27" t="n">
-        <v>304.34</v>
+        <v>112.55</v>
       </c>
       <c r="G27" t="n">
-        <v>173.24</v>
+        <v>102.29</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2244,29 +2414,29 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Udenar</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HUDN</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.4697</v>
+        <v>0.0413</v>
       </c>
       <c r="E28" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="F28" t="n">
-        <v>305.32</v>
+        <v>51.59</v>
       </c>
       <c r="G28" t="n">
-        <v>173.8</v>
+        <v>46.88</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2274,32 +2444,4592 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F29" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="G29" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2249</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F30" t="n">
+        <v>281.17</v>
+      </c>
+      <c r="G30" t="n">
+        <v>255.53</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F31" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="G31" t="n">
+        <v>170.35</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F32" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="G32" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F33" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="G33" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F34" t="n">
+        <v>225.08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>204.55</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F35" t="n">
+        <v>112.54</v>
+      </c>
+      <c r="G35" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F36" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="G36" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F37" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="G37" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F38" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="G38" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F39" t="n">
+        <v>187.46</v>
+      </c>
+      <c r="G39" t="n">
+        <v>170.36</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F40" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="G40" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F41" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="G41" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F42" t="n">
+        <v>293.36</v>
+      </c>
+      <c r="G42" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F43" t="n">
+        <v>239.37</v>
+      </c>
+      <c r="G43" t="n">
+        <v>217.54</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E44" t="n">
+        <v>114</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>101.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="E45" t="n">
+        <v>114</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50.74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F46" t="n">
+        <v>436.09</v>
+      </c>
+      <c r="G46" t="n">
+        <v>396.32</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F47" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="G47" t="n">
+        <v>323.39</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="E48" t="n">
+        <v>114</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>150.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="E49" t="n">
+        <v>114</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>75.42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F50" t="n">
+        <v>473.16</v>
+      </c>
+      <c r="G50" t="n">
+        <v>430.01</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F51" t="n">
+        <v>466.97</v>
+      </c>
+      <c r="G51" t="n">
+        <v>424.38</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F52" t="n">
+        <v>443.48</v>
+      </c>
+      <c r="G52" t="n">
+        <v>403.03</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F53" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="G53" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F58" t="n">
+        <v>238.66</v>
+      </c>
+      <c r="G58" t="n">
+        <v>216.89</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F59" t="n">
+        <v>500.05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>454.45</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>7</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1249.99</v>
+      </c>
+      <c r="F60" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="G60" t="n">
+        <v>174.19</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="E61" t="n">
+        <v>114</v>
+      </c>
+      <c r="F61" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>114.05</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F62" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="G62" t="n">
+        <v>167.48</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F63" t="n">
+        <v>386.13</v>
+      </c>
+      <c r="G63" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1249.99</v>
+      </c>
+      <c r="F64" t="n">
+        <v>148.01</v>
+      </c>
+      <c r="G64" t="n">
+        <v>134.51</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="E65" t="n">
+        <v>114</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>88.06999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>8</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="E66" t="n">
+        <v>114</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F67" t="n">
+        <v>401.37</v>
+      </c>
+      <c r="G67" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>8</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="E68" t="n">
+        <v>114</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="E69" t="n">
+        <v>114</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50.33</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>8</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="E70" t="n">
+        <v>114</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>51.42</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>8</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1247.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1133.73</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>8</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="E72" t="n">
+        <v>114</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>225.34</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>8</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="E73" t="n">
+        <v>114</v>
+      </c>
+      <c r="F73" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>156.44</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>9</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F74" t="n">
+        <v>329.31</v>
+      </c>
+      <c r="G74" t="n">
+        <v>299.27</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>9</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.4655</v>
+      </c>
+      <c r="E75" t="n">
+        <v>114</v>
+      </c>
+      <c r="F75" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1664.76</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>9</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F76" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="G76" t="n">
+        <v>226.54</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F77" t="n">
+        <v>118.16</v>
+      </c>
+      <c r="G77" t="n">
+        <v>107.39</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F78" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G78" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>9</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="E79" t="n">
+        <v>114</v>
+      </c>
+      <c r="F79" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>177.02</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F80" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G80" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>9</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G81" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>10</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.5963000000000001</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F82" t="n">
+        <v>745.34</v>
+      </c>
+      <c r="G82" t="n">
+        <v>677.37</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>10</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1.8514</v>
+      </c>
+      <c r="E83" t="n">
+        <v>114</v>
+      </c>
+      <c r="F83" t="n">
+        <v>211.06</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2103.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>10</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F84" t="n">
+        <v>218.61</v>
+      </c>
+      <c r="G84" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>10</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.0801</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F85" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="G85" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>10</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F86" t="n">
+        <v>203.21</v>
+      </c>
+      <c r="G86" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>10</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.5048</v>
+      </c>
+      <c r="E87" t="n">
+        <v>114</v>
+      </c>
+      <c r="F87" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>573.41</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>10</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F88" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>10</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F89" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="G89" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>11</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F90" t="n">
+        <v>453.48</v>
+      </c>
+      <c r="G90" t="n">
+        <v>412.12</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>11</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2.2123</v>
+      </c>
+      <c r="E91" t="n">
+        <v>114</v>
+      </c>
+      <c r="F91" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2513.13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>11</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F92" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="G92" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>11</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F93" t="n">
+        <v>193.79</v>
+      </c>
+      <c r="G93" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>11</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F94" t="n">
+        <v>191.43</v>
+      </c>
+      <c r="G94" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>11</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.9339</v>
+      </c>
+      <c r="E95" t="n">
+        <v>114</v>
+      </c>
+      <c r="F95" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1060.88</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>11</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F96" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="G96" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>11</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F97" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="G97" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>12</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F98" t="n">
+        <v>110.99</v>
+      </c>
+      <c r="G98" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>12</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1.6916</v>
+      </c>
+      <c r="E99" t="n">
+        <v>114</v>
+      </c>
+      <c r="F99" t="n">
+        <v>192.84</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1921.62</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>12</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F100" t="n">
+        <v>234.98</v>
+      </c>
+      <c r="G100" t="n">
+        <v>213.55</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>12</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F101" t="n">
+        <v>156.18</v>
+      </c>
+      <c r="G101" t="n">
+        <v>141.93</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>12</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F102" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="G102" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>12</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1.2817</v>
+      </c>
+      <c r="E103" t="n">
+        <v>114</v>
+      </c>
+      <c r="F103" t="n">
+        <v>146.12</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1456.06</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>12</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F104" t="n">
+        <v>178.05</v>
+      </c>
+      <c r="G104" t="n">
+        <v>161.81</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>12</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F105" t="n">
+        <v>118.34</v>
+      </c>
+      <c r="G105" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>13</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F106" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="G106" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>13</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="E107" t="n">
+        <v>114</v>
+      </c>
+      <c r="F107" t="n">
+        <v>203.38</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2026.68</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F108" t="n">
+        <v>228.97</v>
+      </c>
+      <c r="G108" t="n">
+        <v>208.09</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>13</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F109" t="n">
+        <v>152.55</v>
+      </c>
+      <c r="G109" t="n">
+        <v>138.63</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>13</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F110" t="n">
+        <v>286.76</v>
+      </c>
+      <c r="G110" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>13</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="E111" t="n">
+        <v>114</v>
+      </c>
+      <c r="F111" t="n">
+        <v>162.66</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1620.87</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>13</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F112" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="G112" t="n">
+        <v>166.42</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>13</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F113" t="n">
+        <v>122</v>
+      </c>
+      <c r="G113" t="n">
+        <v>110.88</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>14</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F114" t="n">
+        <v>548.27</v>
+      </c>
+      <c r="G114" t="n">
+        <v>498.27</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>14</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1.8947</v>
+      </c>
+      <c r="E115" t="n">
+        <v>114</v>
+      </c>
+      <c r="F115" t="n">
+        <v>216</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2152.37</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>14</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F116" t="n">
+        <v>159.31</v>
+      </c>
+      <c r="G116" t="n">
+        <v>144.78</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>14</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F117" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="G117" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>14</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F118" t="n">
+        <v>396.54</v>
+      </c>
+      <c r="G118" t="n">
+        <v>360.38</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>14</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1.3704</v>
+      </c>
+      <c r="E119" t="n">
+        <v>114</v>
+      </c>
+      <c r="F119" t="n">
+        <v>156.22</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1556.72</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>14</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F120" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="G120" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>14</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F121" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="G121" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
         <v>15</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Udenar</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cesmag</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.4717</v>
-      </c>
-      <c r="E29" t="n">
-        <v>280</v>
-      </c>
-      <c r="F29" t="n">
-        <v>132.06</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>174.51</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="E122" t="n">
+        <v>114</v>
+      </c>
+      <c r="F122" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>693.55</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>15</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1.2151</v>
+      </c>
+      <c r="E123" t="n">
+        <v>114</v>
+      </c>
+      <c r="F123" t="n">
+        <v>138.52</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1380.38</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>15</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F124" t="n">
+        <v>162.99</v>
+      </c>
+      <c r="G124" t="n">
+        <v>148.13</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>15</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.0668</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F125" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>15</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="E126" t="n">
+        <v>114</v>
+      </c>
+      <c r="F126" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>457.83</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>15</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="E127" t="n">
+        <v>114</v>
+      </c>
+      <c r="F127" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>911.24</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>15</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F128" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>15</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F129" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="G129" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>16</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F130" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="G130" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>16</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="E131" t="n">
+        <v>114</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>16</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="E132" t="n">
+        <v>114</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>16</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1.0029</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1253.63</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1139.3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>16</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="E134" t="n">
+        <v>114</v>
+      </c>
+      <c r="F134" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>253.83</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>16</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="E135" t="n">
+        <v>114</v>
+      </c>
+      <c r="F135" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>173.42</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>16</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F136" t="n">
+        <v>542.6</v>
+      </c>
+      <c r="G136" t="n">
+        <v>493.12</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>16</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>114</v>
+      </c>
+      <c r="F137" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>109.86</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>16</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>114</v>
+      </c>
+      <c r="F138" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>75.06</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>17</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="E139" t="n">
+        <v>114</v>
+      </c>
+      <c r="F139" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>180.38</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>17</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F140" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="G140" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>17</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="E141" t="n">
+        <v>733.74</v>
+      </c>
+      <c r="F141" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="G141" t="n">
+        <v>77.91</v>
+      </c>
+      <c r="H141" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>17</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="E142" t="n">
+        <v>114</v>
+      </c>
+      <c r="F142" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>148.86</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>17</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="E143" t="n">
+        <v>114</v>
+      </c>
+      <c r="F143" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>150.29</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>18</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="E144" t="n">
+        <v>763.2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="G144" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="H144" t="n">
+        <v>64.25</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>18</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F145" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="G145" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>18</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="E146" t="n">
+        <v>114</v>
+      </c>
+      <c r="F146" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>167.38</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>18</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="E147" t="n">
+        <v>114</v>
+      </c>
+      <c r="F147" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>167.42</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>18</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="E148" t="n">
+        <v>114</v>
+      </c>
+      <c r="F148" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>170.59</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>19</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="E149" t="n">
+        <v>114</v>
+      </c>
+      <c r="F149" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>234.57</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>19</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1032.23</v>
+      </c>
+      <c r="F150" t="n">
+        <v>148.31</v>
+      </c>
+      <c r="G150" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="H150" t="n">
+        <v>31.29</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>19</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1075.89</v>
+      </c>
+      <c r="F151" t="n">
+        <v>154.57</v>
+      </c>
+      <c r="G151" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="H151" t="n">
+        <v>25.01</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>19</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="E152" t="n">
+        <v>114</v>
+      </c>
+      <c r="F152" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>211.95</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>19</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.1972</v>
+      </c>
+      <c r="E153" t="n">
+        <v>114</v>
+      </c>
+      <c r="F153" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>224.02</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>20</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="E154" t="n">
+        <v>704.16</v>
+      </c>
+      <c r="F154" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="G154" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="H154" t="n">
+        <v>92.3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>20</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="E155" t="n">
+        <v>114</v>
+      </c>
+      <c r="F155" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>210.81</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>20</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="E156" t="n">
+        <v>114</v>
+      </c>
+      <c r="F156" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>215.37</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>20</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="E157" t="n">
+        <v>114</v>
+      </c>
+      <c r="F157" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>221.88</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>21</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F158" t="n">
+        <v>160.78</v>
+      </c>
+      <c r="G158" t="n">
+        <v>146.11</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>21</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F159" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="G159" t="n">
+        <v>146</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>21</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F160" t="n">
+        <v>106.14</v>
+      </c>
+      <c r="G160" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>21</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F161" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="G161" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>21</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F162" t="n">
+        <v>459.55</v>
+      </c>
+      <c r="G162" t="n">
+        <v>417.64</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>21</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F163" t="n">
+        <v>459.19</v>
+      </c>
+      <c r="G163" t="n">
+        <v>417.31</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>21</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F164" t="n">
+        <v>303.37</v>
+      </c>
+      <c r="G164" t="n">
+        <v>275.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>21</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F165" t="n">
+        <v>205.11</v>
+      </c>
+      <c r="G165" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>22</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F166" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="G166" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>22</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F167" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="G167" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>22</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F168" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="G168" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>22</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E169" t="n">
+        <v>114</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>22.72</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>22</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F170" t="n">
+        <v>402.61</v>
+      </c>
+      <c r="G170" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>22</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F171" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="G171" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>22</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F172" t="n">
+        <v>225.16</v>
+      </c>
+      <c r="G172" t="n">
+        <v>204.63</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>22</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="E173" t="n">
+        <v>114</v>
+      </c>
+      <c r="F173" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>100.56</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>23</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F174" t="n">
+        <v>281.23</v>
+      </c>
+      <c r="G174" t="n">
+        <v>255.58</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>23</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F175" t="n">
+        <v>112.49</v>
+      </c>
+      <c r="G175" t="n">
+        <v>102.23</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>23</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F176" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="G176" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>23</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F177" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="G177" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>23</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F178" t="n">
+        <v>468.77</v>
+      </c>
+      <c r="G178" t="n">
+        <v>426.02</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>23</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F179" t="n">
+        <v>187.51</v>
+      </c>
+      <c r="G179" t="n">
+        <v>170.41</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>23</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F180" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="G180" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>23</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F181" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="G181" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
